--- a/satisfaction_surveys/032_skincare_fragrance_free_preference_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/032_skincare_fragrance_free_preference_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -995,8 +995,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'fragrance-free'}</t>
+          <t>fragrance-free</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Fragrance-free'}</t>
+          <t>Fragrance-free</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'slightly_sensitive'}</t>
+          <t>slightly_sensitive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Slightly sensitive'}</t>
+          <t>Slightly sensitive</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_sensitive'}</t>
+          <t>somewhat_sensitive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat sensitive'}</t>
+          <t>Somewhat sensitive</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'very_sensitive'}</t>
+          <t>very_sensitive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Very sensitive'}</t>
+          <t>Very sensitive</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'severely_sensitive'}</t>
+          <t>severely_sensitive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Severely sensitive'}</t>
+          <t>Severely sensitive</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'acne-prone'}</t>
+          <t>acne-prone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Acne-prone'}</t>
+          <t>Acne-prone</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'sensitive'}</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Sensitive'}</t>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'oily'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Oily'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Dry'}</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'oily'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Oily'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Dry'}</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'creams'}</t>
+          <t>creams</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Creams'}</t>
+          <t>Creams</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'oils'}</t>
+          <t>oils</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Oils'}</t>
+          <t>Oils</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'serums'}</t>
+          <t>serums</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Serums'}</t>
+          <t>Serums</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'moisturizers'}</t>
+          <t>moisturizers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Moisturizers'}</t>
+          <t>Moisturizers</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'aging'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Aging'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'blackheads'}</t>
+          <t>blackheads</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Blackheads'}</t>
+          <t>Blackheads</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'dullness'}</t>
+          <t>dullness</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Dullness'}</t>
+          <t>Dullness</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'pores'}</t>
+          <t>pores</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Pores'}</t>
+          <t>Pores</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'pore_size'}</t>
+          <t>pore_size</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Pore size'}</t>
+          <t>Pore size</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'redness'}</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Redness'}</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'rosacea'}</t>
+          <t>rosacea</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Rosacea'}</t>
+          <t>Rosacea</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'sensitivty'}</t>
+          <t>sensitivty</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Sensitivty'}</t>
+          <t>Sensitivty</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'uneven_tone'}</t>
+          <t>uneven_tone</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Uneven tone'}</t>
+          <t>Uneven tone</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'aging'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Aging'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'blackheads'}</t>
+          <t>blackheads</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Blackheads'}</t>
+          <t>Blackheads</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'dullness'}</t>
+          <t>dullness</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Dullness'}</t>
+          <t>Dullness</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'pores'}</t>
+          <t>pores</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Pores'}</t>
+          <t>Pores</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'pore_size'}</t>
+          <t>pore_size</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Pore size'}</t>
+          <t>Pore size</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'redness'}</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Redness'}</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'rosacea'}</t>
+          <t>rosacea</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Rosacea'}</t>
+          <t>Rosacea</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'sensitivity'}</t>
+          <t>sensitivity</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Sensitivity'}</t>
+          <t>Sensitivity</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'uneven_tone'}</t>
+          <t>uneven_tone</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Uneven tone'}</t>
+          <t>Uneven tone</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'aging'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Aging'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'blackheads'}</t>
+          <t>blackheads</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Blackheads'}</t>
+          <t>Blackheads</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'dullness'}</t>
+          <t>dullness</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'Dullness'}</t>
+          <t>Dullness</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'pores'}</t>
+          <t>pores</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'Pores'}</t>
+          <t>Pores</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'pore_size'}</t>
+          <t>pore_size</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'Pore size'}</t>
+          <t>Pore size</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'redness'}</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'Redness'}</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'rosacea'}</t>
+          <t>rosacea</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'Rosacea'}</t>
+          <t>Rosacea</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'sensitivity'}</t>
+          <t>sensitivity</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'Sensitivity'}</t>
+          <t>Sensitivity</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'uneven_tone'}</t>
+          <t>uneven_tone</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'Uneven tone'}</t>
+          <t>Uneven tone</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'aging'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'Aging'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_'blackheads'}</t>
+          <t>blackheads</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 'Blackheads'}</t>
+          <t>Blackheads</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_'dullness'}</t>
+          <t>dullness</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 'Dullness'}</t>
+          <t>Dullness</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_'pores'}</t>
+          <t>pores</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 'Pores'}</t>
+          <t>Pores</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_'pore_size'}</t>
+          <t>pore_size</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 'Pore size'}</t>
+          <t>Pore size</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_'redness'}</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 'Redness'}</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_'rosacea'}</t>
+          <t>rosacea</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 'Rosacea'}</t>
+          <t>Rosacea</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_'sensitivity'}</t>
+          <t>sensitivity</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 'Sensitivity'}</t>
+          <t>Sensitivity</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_'uneven_tone'}</t>
+          <t>uneven_tone</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 'Uneven tone'}</t>
+          <t>Uneven tone</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'value':_'oils'}</t>
+          <t>oils</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'value': 'Oils'}</t>
+          <t>Oils</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'value':_'serums'}</t>
+          <t>serums</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'value': 'Serums'}</t>
+          <t>Serums</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'value':_'moisturizers'}</t>
+          <t>moisturizers</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'value': 'Moisturizers'}</t>
+          <t>Moisturizers</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'value':_'exfoliants'}</t>
+          <t>exfoliants</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'value': 'Exfoliants'}</t>
+          <t>Exfoliants</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2197,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2248,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
